--- a/docs/fondo-archivo-madre-ejemplo.xlsx
+++ b/docs/fondo-archivo-madre-ejemplo.xlsx
@@ -1,42 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="instrucciones" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="valor_cuotaparte" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="posiciones" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="fondo" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="clientes" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="movimientos" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="instrucciones" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="valor_cuotaparte" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="posiciones" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="fondo" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="clientes" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="movimientos" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
   <si>
-    <t xml:space="preserve">ARCHIVO MADRE — FONDO PRIVADO (EJEMPLO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Este archivo es la fuente de carga del portal de clientes. La app NO lo lee en vivo:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">un proceso de importacion lo valida y vuelca los datos a la base de datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMO LEER LOS COLORES DE LAS CELDAS:</t>
+    <t>ARCHIVO MADRE — FONDO PRIVADO (EJEMPLO)</t>
+  </si>
+  <si>
+    <t>Este archivo es la fuente de carga del portal de clientes. La app NO lo lee en vivo:</t>
+  </si>
+  <si>
+    <t>un proceso de importacion lo valida y vuelca los datos a la base de datos.</t>
+  </si>
+  <si>
+    <t>COMO LEER LOS COLORES DE LAS CELDAS:</t>
   </si>
   <si>
     <t xml:space="preserve">   • Texto AZUL  = dato que el administrador carga a mano.</t>
@@ -48,7 +42,7 @@
     <t xml:space="preserve">   • Texto VERDE = se calcula solo (formula que toma datos de otra hoja).</t>
   </si>
   <si>
-    <t xml:space="preserve">REGLAS PARA QUE LA APP LO LEA SIN ERRORES:</t>
+    <t>REGLAS PARA QUE LA APP LO LEA SIN ERRORES:</t>
   </si>
   <si>
     <t xml:space="preserve">   • Una sola fila de encabezados (fila 1). Los datos arrancan en la fila 2.</t>
@@ -63,7 +57,7 @@
     <t xml:space="preserve">   • Para agregar datos nuevos (un mes, un movimiento) se agrega una FILA, nunca una hoja nueva.</t>
   </si>
   <si>
-    <t xml:space="preserve">SEGURIDAD — IMPORTANTE:</t>
+    <t>SEGURIDAD — IMPORTANTE:</t>
   </si>
   <si>
     <t xml:space="preserve">   • Las contraseñas NUNCA van en este archivo. El login lo maneja el sistema de autenticacion.</t>
@@ -72,7 +66,7 @@
     <t xml:space="preserve">   • Cada cliente se vincula por su 'cliente_id' / 'email'.</t>
   </si>
   <si>
-    <t xml:space="preserve">HOJAS DEL ARCHIVO:</t>
+    <t>HOJAS DEL ARCHIVO:</t>
   </si>
   <si>
     <t xml:space="preserve">   fondo            → corte general del fondo (total, cuotaparte, cuotapartes emitidas).</t>
@@ -90,262 +84,238 @@
     <t xml:space="preserve">   movimientos      → aportes y retiros (una fila por movimiento).</t>
   </si>
   <si>
-    <t xml:space="preserve">La cantidad de cuotapartes y el valor de la inversion de cada cliente NO se cargan:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">la app los deriva a partir de los movimientos y del historico de la cuotaparte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_cuotaparte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ticker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tipo_instrumento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sector</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cantidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">precio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_mercado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apple Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tecnologia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSFT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nvidia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETF S&amp;P 500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diversificado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AL30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bono Soberano AL30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renta Fija</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GGAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupo Galicia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financiero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSLA-P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Put Tesla (cobertura)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opcion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derivados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_total_fondo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cuotapartes_totales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cliente_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLI-0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Perez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juan@ejemplo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">si</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLI-0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Gonzalez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maria@ejemplo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLI-0003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos Diaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carlos@ejemplo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cuotapartes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">retiro</t>
+    <t>La cantidad de cuotapartes y el valor de la inversion de cada cliente NO se cargan:</t>
+  </si>
+  <si>
+    <t>la app los deriva a partir de los movimientos y del historico de la cuotaparte.</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>valor_cuotaparte</t>
+  </si>
+  <si>
+    <t>ticker</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>tipo_instrumento</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>cantidad</t>
+  </si>
+  <si>
+    <t>precio</t>
+  </si>
+  <si>
+    <t>valor_mercado</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Apple Inc.</t>
+  </si>
+  <si>
+    <t>Accion</t>
+  </si>
+  <si>
+    <t>Tecnologia</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
+    <t>SPY</t>
+  </si>
+  <si>
+    <t>ETF S&amp;P 500</t>
+  </si>
+  <si>
+    <t>ETF</t>
+  </si>
+  <si>
+    <t>Diversificado</t>
+  </si>
+  <si>
+    <t>AL30</t>
+  </si>
+  <si>
+    <t>Bono Soberano AL30</t>
+  </si>
+  <si>
+    <t>Bono</t>
+  </si>
+  <si>
+    <t>Renta Fija</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>Grupo Galicia</t>
+  </si>
+  <si>
+    <t>Financiero</t>
+  </si>
+  <si>
+    <t>TSLA-P</t>
+  </si>
+  <si>
+    <t>Put Tesla (cobertura)</t>
+  </si>
+  <si>
+    <t>Opcion</t>
+  </si>
+  <si>
+    <t>Derivados</t>
+  </si>
+  <si>
+    <t>valor_total_fondo</t>
+  </si>
+  <si>
+    <t>cuotapartes_totales</t>
+  </si>
+  <si>
+    <t>cliente_id</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>activo</t>
+  </si>
+  <si>
+    <t>CLI-0001</t>
+  </si>
+  <si>
+    <t>Juan Perez</t>
+  </si>
+  <si>
+    <t>juan@ejemplo.com</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>CLI-0002</t>
+  </si>
+  <si>
+    <t>Maria Gonzalez</t>
+  </si>
+  <si>
+    <t>maria@ejemplo.com</t>
+  </si>
+  <si>
+    <t>CLI-0003</t>
+  </si>
+  <si>
+    <t>Carlos Diaz</t>
+  </si>
+  <si>
+    <t>benjaminschmittt@gmail.com</t>
+  </si>
+  <si>
+    <t>tipo</t>
+  </si>
+  <si>
+    <t>monto</t>
+  </si>
+  <si>
+    <t>cuotapartes</t>
+  </si>
+  <si>
+    <t>aporte</t>
+  </si>
+  <si>
+    <t>retiro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="\$#,##0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="$#,##0"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <b/>
+      <charset val="1"/>
+      <color rgb="FF00296B"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
+      <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <charset val="1"/>
+      <color rgb="FF0000FF"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF008000"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF00296B"/>
+      <b/>
+      <charset val="1"/>
+      <color rgb="FFB91C1C"/>
+      <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FFB91C1C"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <charset val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFB91C1C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFB91C1C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -363,14 +333,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -386,169 +356,73 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF00296B"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFB91C1C"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -728,173 +602,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
+    <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="17.35" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="21.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>23</v>
       </c>
@@ -902,132 +765,123 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+    <row r="2" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
         <v>45869</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="n">
+    <row r="3" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
         <v>45900</v>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="10">
         <v>102.3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="n">
+    <row r="4" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
         <v>45930</v>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="10">
         <v>101.1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
+    <row r="5" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
         <v>45961</v>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="10">
         <v>105.6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+    <row r="6" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
         <v>45991</v>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="10">
         <v>108.2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
+    <row r="7" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>46022</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="10">
         <v>110.5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+    <row r="8" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
         <v>46053</v>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="10">
         <v>109</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
+    <row r="9" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
         <v>46081</v>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="10">
         <v>113.4</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="n">
+    <row r="10" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
         <v>46112</v>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="10">
         <v>117.8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="n">
+    <row r="11" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
         <v>46142</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="10">
         <v>119.2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="n">
+    <row r="12" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
         <v>46173</v>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="10">
         <v>124.6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="n">
+    <row r="13" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
         <v>46203</v>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="10">
         <v>128.9</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="21.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>23</v>
       </c>
@@ -1053,8 +907,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+    <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
         <v>46203</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1069,19 +923,19 @@
       <c r="E2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="4">
         <v>1000</v>
       </c>
-      <c r="G2" s="11" t="n">
+      <c r="G2" s="11">
         <v>320</v>
       </c>
-      <c r="H2" s="12" t="n">
-        <f aca="false">F2*G2</f>
+      <c r="H2" s="12">
+        <f>F2*G2</f>
         <v>320000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="n">
+    <row r="3" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
         <v>46203</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1096,19 +950,19 @@
       <c r="E3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="4">
         <v>500</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" s="11">
         <v>560</v>
       </c>
-      <c r="H3" s="12" t="n">
-        <f aca="false">F3*G3</f>
+      <c r="H3" s="12">
+        <f>F3*G3</f>
         <v>280000</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="n">
+    <row r="4" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
         <v>46203</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1123,19 +977,19 @@
       <c r="E4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4">
         <v>200</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="11">
         <v>1000</v>
       </c>
-      <c r="H4" s="12" t="n">
-        <f aca="false">F4*G4</f>
+      <c r="H4" s="12">
+        <f>F4*G4</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
+    <row r="5" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
         <v>46203</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1150,19 +1004,19 @@
       <c r="E5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="4">
         <v>500</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="11">
         <v>500</v>
       </c>
-      <c r="H5" s="12" t="n">
-        <f aca="false">F5*G5</f>
+      <c r="H5" s="12">
+        <f>F5*G5</f>
         <v>250000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+    <row r="6" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
         <v>46203</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1177,19 +1031,19 @@
       <c r="E6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="4">
         <v>2000</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="11">
         <v>90</v>
       </c>
-      <c r="H6" s="12" t="n">
-        <f aca="false">F6*G6</f>
+      <c r="H6" s="12">
+        <f>F6*G6</f>
         <v>180000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
+    <row r="7" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
         <v>46203</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1204,19 +1058,19 @@
       <c r="E7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="4">
         <v>2000</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="11">
         <v>60</v>
       </c>
-      <c r="H7" s="12" t="n">
-        <f aca="false">F7*G7</f>
+      <c r="H7" s="12">
+        <f>F7*G7</f>
         <v>120000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+    <row r="8" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
         <v>46203</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1231,43 +1085,35 @@
       <c r="E8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="4">
         <v>2000</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="11">
         <v>25</v>
       </c>
-      <c r="H8" s="12" t="n">
-        <f aca="false">F8*G8</f>
+      <c r="H8" s="12">
+        <f>F8*G8</f>
         <v>50000</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="21.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>23</v>
       </c>
@@ -1281,49 +1127,40 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+    <row r="2" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
         <v>46203</v>
       </c>
-      <c r="B2" s="13" t="n">
-        <f aca="false">SUM(posiciones!H2:H8)</f>
+      <c r="B2" s="13">
+        <f>SUM(posiciones!H2:H8)</f>
         <v>1400000</v>
       </c>
-      <c r="C2" s="14" t="n">
-        <f aca="false">INDEX(valor_cuotaparte!$B:$B,MATCH(A2,valor_cuotaparte!$A:$A,0))</f>
+      <c r="C2" s="14">
+        <f>INDEX(valor_cuotaparte!$B:$B,MATCH(A2,valor_cuotaparte!$A:$A,0))</f>
         <v>128.9</v>
       </c>
-      <c r="D2" s="15" t="n">
-        <f aca="false">B2/C2</f>
+      <c r="D2" s="15">
+        <f>B2/C2</f>
         <v>10861.1326609775</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="21.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>57</v>
       </c>
@@ -1337,7 +1174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>60</v>
       </c>
@@ -1351,7 +1188,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>64</v>
       </c>
@@ -1365,7 +1202,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
@@ -1380,31 +1217,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="21.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>57</v>
       </c>
@@ -1421,103 +1250,98 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="9">
         <v>45869</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="16">
         <v>100000</v>
       </c>
-      <c r="E2" s="14" t="n">
-        <f aca="false">D2/INDEX(valor_cuotaparte!$B:$B,MATCH(B2,valor_cuotaparte!$A:$A,0))</f>
+      <c r="E2" s="14">
+        <f>D2/INDEX(valor_cuotaparte!$B:$B,MATCH(B2,valor_cuotaparte!$A:$A,0))</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="9">
         <v>46053</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="16">
         <v>50000</v>
       </c>
-      <c r="E3" s="14" t="n">
-        <f aca="false">D3/INDEX(valor_cuotaparte!$B:$B,MATCH(B3,valor_cuotaparte!$A:$A,0))</f>
+      <c r="E3" s="14">
+        <f>D3/INDEX(valor_cuotaparte!$B:$B,MATCH(B3,valor_cuotaparte!$A:$A,0))</f>
         <v>458.715596330275</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="9">
         <v>45930</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="16">
         <v>200000</v>
       </c>
-      <c r="E4" s="14" t="n">
-        <f aca="false">D4/INDEX(valor_cuotaparte!$B:$B,MATCH(B4,valor_cuotaparte!$A:$A,0))</f>
+      <c r="E4" s="14">
+        <f>D4/INDEX(valor_cuotaparte!$B:$B,MATCH(B4,valor_cuotaparte!$A:$A,0))</f>
         <v>1978.2393669634</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="9">
         <v>46112</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="16">
         <v>30000</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <f aca="false">D5/INDEX(valor_cuotaparte!$B:$B,MATCH(B5,valor_cuotaparte!$A:$A,0))</f>
+      <c r="E5" s="14">
+        <f>D5/INDEX(valor_cuotaparte!$B:$B,MATCH(B5,valor_cuotaparte!$A:$A,0))</f>
         <v>254.668930390492</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="9">
         <v>45991</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="16">
         <v>80000</v>
       </c>
-      <c r="E6" s="14" t="n">
-        <f aca="false">D6/INDEX(valor_cuotaparte!$B:$B,MATCH(B6,valor_cuotaparte!$A:$A,0))</f>
+      <c r="E6" s="14">
+        <f>D6/INDEX(valor_cuotaparte!$B:$B,MATCH(B6,valor_cuotaparte!$A:$A,0))</f>
         <v>739.371534195934</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>